--- a/data/product_master.xlsx
+++ b/data/product_master.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제품마스터" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,28 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,12 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,2117 +413,2321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>대분류내역</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>중분류내역</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>소분류내역</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>제품코드</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>제품명</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>원가</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>체어원</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>HLX-CH-C1-BLK</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Chair One Black</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" t="n">
         <v>169000</v>
       </c>
+      <c r="G2" t="n">
+        <v>125185</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>체어원</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>HLX-CH-C1-TAN</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Chair One Tan</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="n">
         <v>169000</v>
       </c>
+      <c r="G3" t="n">
+        <v>125185</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>체어원</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>HLX-CH-C1-NVY</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Chair One Navy</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" t="n">
         <v>169000</v>
       </c>
+      <c r="G4" t="n">
+        <v>125185</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>체어원</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>HLX-CH-C1L-BLK</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Chair One L Black</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" t="n">
         <v>189000</v>
       </c>
+      <c r="G5" t="n">
+        <v>140000</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>체어원</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>HLX-CH-C1L-TAN</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Chair One L Tan</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" t="n">
         <v>189000</v>
       </c>
+      <c r="G6" t="n">
+        <v>140000</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>체어투</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>HLX-CH-C2-BLK</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Chair Two Black</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" t="n">
         <v>219000</v>
       </c>
+      <c r="G7" t="n">
+        <v>162222</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>체어투</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>HLX-CH-C2-GRN</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Chair Two Green</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" t="n">
         <v>219000</v>
       </c>
+      <c r="G8" t="n">
+        <v>162222</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>체어투</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>HLX-CH-C2LT-BLK</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Chair Two Light Black</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" t="n">
         <v>229000</v>
       </c>
+      <c r="G9" t="n">
+        <v>169630</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>체어제로</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>HLX-CH-C0-BLK</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Chair Zero Black</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" t="n">
         <v>259000</v>
       </c>
+      <c r="G10" t="n">
+        <v>191852</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>체어제로</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>HLX-CH-C0-GRY</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Chair Zero Grey</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" t="n">
         <v>259000</v>
       </c>
+      <c r="G11" t="n">
+        <v>191852</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>체어제로</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>HLX-CH-C0LT-BLK</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Chair Zero Lightweight Black</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" t="n">
         <v>299000</v>
       </c>
+      <c r="G12" t="n">
+        <v>221481</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>선셋체어</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>HLX-CH-SS-BLK</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Sunset Chair Black</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" t="n">
         <v>219000</v>
       </c>
+      <c r="G13" t="n">
+        <v>162222</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>선셋체어</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>HLX-CH-SS-TAN</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Sunset Chair Tan</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" t="n">
         <v>219000</v>
       </c>
+      <c r="G14" t="n">
+        <v>162222</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>선셋체어</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>HLX-CH-SS-NVY</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Sunset Chair Navy</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" t="n">
         <v>219000</v>
       </c>
+      <c r="G15" t="n">
+        <v>162222</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>선셋체어LT</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>HLX-CH-SSLT-BLK</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Sunset Chair LT Black</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" t="n">
         <v>249000</v>
       </c>
+      <c r="G16" t="n">
+        <v>184444</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>체어원로커</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>HLX-CH-C1R-BLK</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Chair One Rocker Black</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" t="n">
         <v>249000</v>
       </c>
+      <c r="G17" t="n">
+        <v>184444</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>체어원로커</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>HLX-CH-C1R-TAN</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Chair One Rocker Tan</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" t="n">
         <v>249000</v>
       </c>
+      <c r="G18" t="n">
+        <v>184444</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>그라운드체어</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>HLX-CH-GR-BLK</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Ground Chair Black</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" t="n">
         <v>149000</v>
       </c>
+      <c r="G19" t="n">
+        <v>110370</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>그라운드체어</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>HLX-CH-GR-GRN</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Ground Chair Green</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" t="n">
         <v>149000</v>
       </c>
+      <c r="G20" t="n">
+        <v>110370</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>바나나체어</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>HLX-CH-BN-BLK</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Banana Chair Black</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" t="n">
         <v>319000</v>
       </c>
+      <c r="G21" t="n">
+        <v>236296</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>바나나체어</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>HLX-CH-BN-TAN</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Banana Chair Tan</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" t="n">
         <v>319000</v>
       </c>
+      <c r="G22" t="n">
+        <v>236296</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>테이블원</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>HLX-TB-T1-BLK</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Table One Black</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" t="n">
         <v>139000</v>
       </c>
+      <c r="G23" t="n">
+        <v>99286</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>테이블원</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>HLX-TB-T1-GRY</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Table One Grey</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" t="n">
         <v>139000</v>
       </c>
+      <c r="G24" t="n">
+        <v>99286</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>테이블원하드탑</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>HLX-TB-T1HM-BLK</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Table One Hard Top M Black</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" t="n">
         <v>179000</v>
       </c>
+      <c r="G25" t="n">
+        <v>127857</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>테이블원하드탑</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>HLX-TB-T1HL-BLK</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Table One Hard Top L Black</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" t="n">
         <v>219000</v>
       </c>
+      <c r="G26" t="n">
+        <v>156429</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>사이드테이블</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>HLX-TB-ST-BLK</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Side Table Black</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" t="n">
         <v>89000</v>
       </c>
+      <c r="G27" t="n">
+        <v>63571</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>사이드테이블</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>HLX-TB-ST-GRY</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Side Table Grey</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" t="n">
         <v>89000</v>
       </c>
+      <c r="G28" t="n">
+        <v>63571</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>테이블원홈</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>HLX-TB-T1HO-BLK</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Table One Home Black</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" t="n">
         <v>189000</v>
       </c>
+      <c r="G29" t="n">
+        <v>135000</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>코트</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>코트원</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>HLX-CT-C1-BLK</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Cot One Convertible Black</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" t="n">
         <v>289000</v>
       </c>
+      <c r="G30" t="n">
+        <v>206429</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>코트</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>코트원</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>HLX-CT-C1-TAN</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Cot One Convertible Tan</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" t="n">
         <v>289000</v>
       </c>
+      <c r="G31" t="n">
+        <v>206429</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>코트</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>코트원플러스</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>HLX-CT-C1P-BLK</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Cot One Convertible Plus Black</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" t="n">
         <v>339000</v>
       </c>
+      <c r="G32" t="n">
+        <v>242143</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>코트</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>라이트코트</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>HLX-CT-LT-BLK</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Lite Cot Black</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" t="n">
         <v>199000</v>
       </c>
+      <c r="G33" t="n">
+        <v>142143</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>코트</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>라이트코트</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>HLX-CT-LT-GRY</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Lite Cot Grey</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" t="n">
         <v>199000</v>
       </c>
+      <c r="G34" t="n">
+        <v>142143</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>코트&amp;가이드</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>선라운저</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>HLX-CG-SL-BLK</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Sundown Lounger Black</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" t="n">
         <v>359000</v>
       </c>
+      <c r="G35" t="n">
+        <v>256429</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>코트&amp;가이드</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>선라운저</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>HLX-CG-SL-TAN</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Sundown Lounger Tan</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" t="n">
         <v>359000</v>
       </c>
+      <c r="G36" t="n">
+        <v>256429</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>코트&amp;가이드</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>풋레스트</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>HLX-CG-FR-BLK</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Foot Rest Black</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" t="n">
         <v>89000</v>
       </c>
+      <c r="G37" t="n">
+        <v>63571</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>코트&amp;가이드</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>풋레스트</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>HLX-CG-FR-GRY</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Foot Rest Grey</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" t="n">
         <v>89000</v>
       </c>
+      <c r="G38" t="n">
+        <v>63571</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>코트&amp;가이드</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>사이드보드</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>HLX-CG-SB-BLK</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Side Board Black</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" t="n">
         <v>129000</v>
       </c>
+      <c r="G39" t="n">
+        <v>92143</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>필드퍼니처</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>비비박스</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>HLX-FF-BVM-BLK</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Bivi Box M Black</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" t="n">
         <v>149000</v>
       </c>
+      <c r="G40" t="n">
+        <v>106429</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>필드퍼니처</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>비비박스</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>HLX-FF-BVL-BLK</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Bivi Box L Black</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" t="n">
         <v>179000</v>
       </c>
+      <c r="G41" t="n">
+        <v>127857</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>필드퍼니처</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>큐브</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>HLX-FF-CB-BLK</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Cube Black</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" t="n">
         <v>99000</v>
       </c>
+      <c r="G42" t="n">
+        <v>70714</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>필드퍼니처</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>큐브</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>HLX-FF-CB-TAN</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Cube Tan</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" t="n">
         <v>99000</v>
       </c>
+      <c r="G43" t="n">
+        <v>70714</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>스토리지&amp;캐리</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>스토리지박스</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>HLX-SC-SBS-BLK</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Storage Box S Black</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" t="n">
         <v>79000</v>
       </c>
+      <c r="G44" t="n">
+        <v>56429</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>스토리지&amp;캐리</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>스토리지박스</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>HLX-SC-SBM-BLK</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Storage Box M Black</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" t="n">
         <v>99000</v>
       </c>
+      <c r="G45" t="n">
+        <v>70714</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>스토리지&amp;캐리</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>스토리지박스</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>HLX-SC-SBL-BLK</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Storage Box L Black</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" t="n">
         <v>129000</v>
       </c>
+      <c r="G46" t="n">
+        <v>92143</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>스토리지&amp;캐리</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>캐리백</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>HLX-SC-CB1-BLK</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Chair One Carry Bag Black</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" t="n">
         <v>59000</v>
       </c>
+      <c r="G47" t="n">
+        <v>42143</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>스토리지&amp;캐리</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>캐리백</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>HLX-SC-CBT-BLK</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Table One Carry Bag Black</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" t="n">
         <v>49000</v>
       </c>
+      <c r="G48" t="n">
+        <v>35000</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>V.TAR</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>HLX-TN-VT1-BLK</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>V.TAR P1 Black</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" t="n">
         <v>590000</v>
       </c>
+      <c r="G49" t="n">
+        <v>393333</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>V.TAR</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>HLX-TN-VT1-CYT</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>V.TAR P1 Coyote Tan</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" t="n">
         <v>590000</v>
       </c>
+      <c r="G50" t="n">
+        <v>393333</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>V.TAR</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>HLX-TN-VT2-BLK</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>V.TAR P2 Black</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" t="n">
         <v>690000</v>
       </c>
+      <c r="G51" t="n">
+        <v>460000</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>V.TAR</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>HLX-TN-VT2-CYT</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>V.TAR P2 Coyote Tan</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" t="n">
         <v>690000</v>
       </c>
+      <c r="G52" t="n">
+        <v>460000</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>V.TAP</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>HLX-TN-VP2-BLK</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>V.TAP 2P Black</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" t="n">
         <v>890000</v>
       </c>
+      <c r="G53" t="n">
+        <v>593333</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>V.TAP</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>HLX-TN-VP2-GRN</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>V.TAP 2P Green</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" t="n">
         <v>890000</v>
       </c>
+      <c r="G54" t="n">
+        <v>593333</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>V.TAP</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>HLX-TN-VP4-BLK</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>V.TAP 4P Black</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" t="n">
         <v>1190000</v>
       </c>
+      <c r="G55" t="n">
+        <v>793333</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>V.TARP</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>HLX-TN-TARP-CYT</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>V.TARP Coyote Tan</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" t="n">
         <v>490000</v>
       </c>
+      <c r="G56" t="n">
+        <v>326667</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>텐트</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>V.TARP</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>HLX-TN-TARP-BLK</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>V.TARP Black</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" t="n">
         <v>490000</v>
       </c>
+      <c r="G57" t="n">
+        <v>326667</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>트레킹폴</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Causeway</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>HLX-TP-CWC-BLK</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Causeway Carbon Black</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" t="n">
         <v>219000</v>
       </c>
+      <c r="G58" t="n">
+        <v>156429</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>트레킹폴</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Causeway</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>HLX-TP-CWA-BLK</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Causeway Aluminum Black</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" t="n">
         <v>169000</v>
       </c>
+      <c r="G59" t="n">
+        <v>120714</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>트레킹폴</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Ridgeline</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>HLX-TP-RDC-BLK</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Ridgeline Carbon Black</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" t="n">
         <v>239000</v>
       </c>
+      <c r="G60" t="n">
+        <v>170714</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>트레킹폴</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Ridgeline</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>HLX-TP-RDC-NVY</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Ridgeline Carbon Navy</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" t="n">
         <v>239000</v>
       </c>
+      <c r="G61" t="n">
+        <v>170714</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>트레킹폴</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Passport</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>HLX-TP-PSC-BLK</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Passport Carbon Black</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" t="n">
         <v>189000</v>
       </c>
+      <c r="G62" t="n">
+        <v>135000</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>액세서리</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>체어부품</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>HLX-AC-BF-SET</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Chair One Ball Feet Set</t>
         </is>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" t="n">
         <v>29000</v>
       </c>
+      <c r="G63" t="n">
+        <v>20714</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>액세서리</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>체어부품</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>HLX-AC-LC-SET</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Chair One Leg Caps Set</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" t="n">
         <v>19000</v>
       </c>
+      <c r="G64" t="n">
+        <v>13571</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>액세서리</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>범용</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>HLX-AC-GS-GRN</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Ground Sheet Green</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" t="n">
         <v>49000</v>
       </c>
+      <c r="G65" t="n">
+        <v>35000</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Helinox</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Helinox</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>액세서리</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>범용</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>HLX-AC-RK-STD</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Repair Kit Standard</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" t="n">
         <v>15000</v>
       </c>
+      <c r="G66" t="n">
+        <v>10714</v>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>HCC</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>캠핑체어</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>HCC-CH-C1-BLK</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>HCC Camp Chair Black</t>
         </is>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" t="n">
         <v>89000</v>
       </c>
+      <c r="G67" t="n">
+        <v>65926</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>HCC</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>캠핑체어</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>HCC-CH-C1-KHK</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>HCC Camp Chair Khaki</t>
         </is>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" t="n">
         <v>89000</v>
       </c>
+      <c r="G68" t="n">
+        <v>65926</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>HCC</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>체어</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>폴딩체어</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>HCC-CH-FD-BLK</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>HCC Folding Chair Black</t>
         </is>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" t="n">
         <v>69000</v>
       </c>
+      <c r="G69" t="n">
+        <v>51111</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>HCC</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>테이블</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>캠핑테이블</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>HCC-TB-C1-BLK</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>HCC Camp Table Black</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F70" t="n">
         <v>79000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>56429</v>
       </c>
     </row>
   </sheetData>
